--- a/artfynd/A 18101-2024 artfynd.xlsx
+++ b/artfynd/A 18101-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>134268100</v>
       </c>
       <c r="B5" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>134268077</v>
       </c>
       <c r="B6" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>134268141</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>134266151</v>
       </c>
       <c r="B8" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>134266213</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>134266010</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>134273527</v>
       </c>
       <c r="B11" t="n">
-        <v>79454</v>
+        <v>79461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>134273531</v>
       </c>
       <c r="B12" t="n">
-        <v>79454</v>
+        <v>79461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>134273526</v>
       </c>
       <c r="B13" t="n">
-        <v>79454</v>
+        <v>79461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>134273584</v>
       </c>
       <c r="B14" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>134273518</v>
       </c>
       <c r="B15" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>134273530</v>
       </c>
       <c r="B16" t="n">
-        <v>79454</v>
+        <v>79461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 18101-2024 artfynd.xlsx
+++ b/artfynd/A 18101-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117398727</v>
+        <v>134273526</v>
       </c>
       <c r="B2" t="n">
-        <v>78217</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520809</v>
+        <v>520677</v>
       </c>
       <c r="R2" t="n">
-        <v>6847991</v>
+        <v>6847916</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117398825</v>
+        <v>134273527</v>
       </c>
       <c r="B3" t="n">
-        <v>78216</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,41 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520751</v>
+        <v>520680</v>
       </c>
       <c r="R3" t="n">
-        <v>6847924</v>
+        <v>6847893</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,17 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,27 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117398822</v>
+        <v>134273530</v>
       </c>
       <c r="B4" t="n">
-        <v>78216</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,41 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520810</v>
+        <v>520694</v>
       </c>
       <c r="R4" t="n">
-        <v>6847991</v>
+        <v>6847883</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,17 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134268100</v>
+        <v>134273531</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,37 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520839</v>
+        <v>520696</v>
       </c>
       <c r="R5" t="n">
-        <v>6848005</v>
+        <v>6847884</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,9 +1064,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,22 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134268077</v>
+        <v>117398822</v>
       </c>
       <c r="B6" t="n">
-        <v>79985</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,34 +1114,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Lillskog, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520843</v>
+        <v>520810</v>
       </c>
       <c r="R6" t="n">
-        <v>6847998</v>
+        <v>6847991</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,12 +1172,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,22 +1197,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134268141</v>
+        <v>117398825</v>
       </c>
       <c r="B7" t="n">
-        <v>79123</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,17 +1237,21 @@
           <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Lillskog, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520848</v>
+        <v>520751</v>
       </c>
       <c r="R7" t="n">
-        <v>6848020</v>
+        <v>6847924</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,12 +1278,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,22 +1303,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134266151</v>
+        <v>134266010</v>
       </c>
       <c r="B8" t="n">
-        <v>79985</v>
+        <v>79130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1334,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520778</v>
+        <v>520799</v>
       </c>
       <c r="R8" t="n">
-        <v>6847951</v>
+        <v>6847954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1415,7 @@
         <v>134266213</v>
       </c>
       <c r="B9" t="n">
-        <v>79123</v>
+        <v>79130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134266010</v>
+        <v>134268141</v>
       </c>
       <c r="B10" t="n">
-        <v>79123</v>
+        <v>79130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1528,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520799</v>
+        <v>520848</v>
       </c>
       <c r="R10" t="n">
-        <v>6847954</v>
+        <v>6848020</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134273527</v>
+        <v>134266151</v>
       </c>
       <c r="B11" t="n">
-        <v>79461</v>
+        <v>79992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1601,37 +1617,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öster om Los, Hls</t>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520680</v>
+        <v>520778</v>
       </c>
       <c r="R11" t="n">
-        <v>6847893</v>
+        <v>6847951</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1658,19 +1674,9 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>18:24</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>18:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,22 +1691,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134273531</v>
+        <v>134268077</v>
       </c>
       <c r="B12" t="n">
-        <v>79461</v>
+        <v>79992</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1708,37 +1714,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öster om Los, Hls</t>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520696</v>
+        <v>520843</v>
       </c>
       <c r="R12" t="n">
-        <v>6847884</v>
+        <v>6847998</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1765,19 +1771,9 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>18:27</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>18:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1792,22 +1788,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134273526</v>
+        <v>134273518</v>
       </c>
       <c r="B13" t="n">
-        <v>79461</v>
+        <v>79992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1815,21 +1811,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1839,10 +1835,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520677</v>
+        <v>520735</v>
       </c>
       <c r="R13" t="n">
-        <v>6847916</v>
+        <v>6847993</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1874,7 +1870,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1884,7 +1880,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,7 +1910,7 @@
         <v>134273584</v>
       </c>
       <c r="B14" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134273518</v>
+        <v>117398727</v>
       </c>
       <c r="B15" t="n">
-        <v>79985</v>
+        <v>79085</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2029,37 +2025,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öster om Los, Hls</t>
+          <t>Lillskog, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520735</v>
+        <v>520809</v>
       </c>
       <c r="R15" t="n">
-        <v>6847993</v>
+        <v>6847991</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2083,22 +2083,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>18:12</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>18:12</t>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,22 +2108,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134273530</v>
+        <v>134268100</v>
       </c>
       <c r="B16" t="n">
-        <v>79461</v>
+        <v>79131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2136,37 +2131,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öster om Los, Hls</t>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520694</v>
+        <v>520839</v>
       </c>
       <c r="R16" t="n">
-        <v>6847883</v>
+        <v>6848005</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2193,19 +2188,9 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>18:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,15 +2205,122 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134273512</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Öster om Los, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>520771</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6848022</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18101-2024 artfynd.xlsx
+++ b/artfynd/A 18101-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273526</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273527</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273530</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273531</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398822</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398825</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134266010</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,6 +1546,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134266213</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1603,6 +1648,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134268141</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134266151</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1797,6 +1852,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134268077</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1904,6 +1964,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273518</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2011,6 +2076,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273584</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2117,6 +2187,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398727</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2214,6 +2289,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134268100</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2321,8 +2401,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273512</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>